--- a/customers/alireza.xlsx
+++ b/customers/alireza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>بستنی عاشورا</t>
+  </si>
+  <si>
+    <t>1405/04/19</t>
   </si>
 </sst>
 </file>
@@ -208,13 +211,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -545,9 +548,9 @@
       <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="9">
         <f>A23</f>
-        <v>10450000</v>
+        <v>6450000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -783,18 +786,24 @@
     <row r="17" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <f t="shared" si="0"/>
-        <v>10450000</v>
+        <v>6450000</v>
       </c>
       <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="3"/>
+      <c r="C17" s="6">
+        <v>4000000</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <f t="shared" si="0"/>
-        <v>10450000</v>
+        <v>6450000</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -805,7 +814,7 @@
     <row r="19" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <f t="shared" si="0"/>
-        <v>10450000</v>
+        <v>6450000</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -816,7 +825,7 @@
     <row r="20" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <f t="shared" si="0"/>
-        <v>10450000</v>
+        <v>6450000</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -827,7 +836,7 @@
     <row r="21" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <f t="shared" si="0"/>
-        <v>10450000</v>
+        <v>6450000</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -843,22 +852,22 @@
       </c>
       <c r="C22" s="7">
         <f>SUM(C3:C21)</f>
-        <v>3772000</v>
+        <v>7772000</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="10">
+      <c r="A23" s="11">
         <f>A21</f>
-        <v>10450000</v>
-      </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="9" t="s">
+        <v>6450000</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="10"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
